--- a/data/trans_dic/P1421-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1421-Estudios-trans_dic.xlsx
@@ -664,34 +664,34 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11,82%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>4,45%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>4,11%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,05</t>
+          <t>2,0; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,64</t>
+          <t>0,87; 2,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,3</t>
+          <t>1,25; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,35</t>
+          <t>2,62; 5,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,1</t>
+          <t>4,42; 7,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,35</t>
+          <t>4,86; 7,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,29</t>
+          <t>5,63; 9,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 15,19</t>
+          <t>10,07; 13,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,35</t>
+          <t>3,65; 5,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,1</t>
+          <t>3,31; 5,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,38</t>
+          <t>4,0; 6,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,08</t>
+          <t>7,45; 9,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,63</t>
+          <t>1,24; 2,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,78</t>
+          <t>0,76; 1,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,78</t>
+          <t>0,68; 1,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,61</t>
+          <t>3,9; 6,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,09</t>
+          <t>4,68; 7,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,02</t>
+          <t>3,94; 6,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,83</t>
+          <t>3,89; 5,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,78</t>
+          <t>10,33; 12,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,4</t>
+          <t>3,1; 4,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,63</t>
+          <t>2,38; 3,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,52</t>
+          <t>2,36; 3,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,27</t>
+          <t>7,25; 8,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,12</t>
+          <t>1,99; 4,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,22</t>
+          <t>0,79; 3,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,88</t>
+          <t>2,65; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,65</t>
+          <t>3,83; 8,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,09</t>
+          <t>3,8; 8,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,45</t>
+          <t>3,41; 7,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 12,79</t>
+          <t>8,52; 12,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,04</t>
+          <t>3,4; 6,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,23</t>
+          <t>2,01; 4,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,66</t>
+          <t>2,5; 4,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,66</t>
+          <t>6,03; 8,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,0</t>
+          <t>1,95; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,67</t>
+          <t>0,88; 1,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,89</t>
+          <t>1,04; 1,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,34</t>
+          <t>3,84; 5,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,65</t>
+          <t>4,98; 6,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,21</t>
+          <t>4,61; 6,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,39</t>
+          <t>4,76; 6,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,69</t>
+          <t>10,47; 12,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,59</t>
+          <t>3,64; 4,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,78</t>
+          <t>2,89; 3,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,97</t>
+          <t>3,07; 3,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,4</t>
+          <t>7,41; 8,64</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>96888</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>116702</t>
+          <t>119378</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20041; 41759</t>
+          <t>20660; 40908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9228; 25773</t>
+          <t>8472; 25086</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8970; 24928</t>
+          <t>9450; 24625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15777; 32544</t>
+          <t>15111; 31295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59211; 93385</t>
+          <t>58190; 91996</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62880; 98343</t>
+          <t>65013; 100053</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56102; 92386</t>
+          <t>56018; 92023</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80584; 114217</t>
+          <t>82606; 112819</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85069; 125567</t>
+          <t>85589; 125705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77441; 117867</t>
+          <t>76484; 117046</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71269; 111607</t>
+          <t>69914; 108012</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>101301; 140102</t>
+          <t>104085; 136969</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>107382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>223419</t>
+          <t>249159</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>325887</t>
+          <t>356541</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21161; 44550</t>
+          <t>21058; 44413</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16129; 34898</t>
+          <t>14908; 33572</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14981; 36971</t>
+          <t>14171; 34522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72325; 128426</t>
+          <t>86809; 134202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74357; 112640</t>
+          <t>74265; 111935</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67919; 105561</t>
+          <t>69172; 107223</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77245; 115831</t>
+          <t>77308; 115318</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>155309; 263225</t>
+          <t>224038; 276334</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>101888; 144237</t>
+          <t>101741; 147394</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90438; 135002</t>
+          <t>88458; 131007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98059; 143111</t>
+          <t>95958; 140962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>255786; 374130</t>
+          <t>318737; 393297</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68224</t>
+          <t>75739</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94440</t>
+          <t>104933</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11357; 28256</t>
+          <t>10975; 26615</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7116</t>
+          <t>0; 6651</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4910; 17609</t>
+          <t>4297; 17285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16756; 38038</t>
+          <t>18830; 42367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18849; 41231</t>
+          <t>18224; 39848</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16452; 37081</t>
+          <t>17405; 37595</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19281; 40911</t>
+          <t>18736; 40403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55198; 84469</t>
+          <t>62522; 92752</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34545; 62080</t>
+          <t>34940; 64025</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18038; 39800</t>
+          <t>18862; 40401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27462; 51084</t>
+          <t>27386; 52713</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77658; 113175</t>
+          <t>87132; 126421</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151494</t>
+          <t>159066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>385535</t>
+          <t>421786</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>537029</t>
+          <t>580852</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62800; 98230</t>
+          <t>63733; 98843</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30311; 57087</t>
+          <t>30073; 55514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35814; 63838</t>
+          <t>35157; 62484</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118824; 184047</t>
+          <t>134929; 188280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>170511; 224671</t>
+          <t>168324; 222270</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>162943; 220587</t>
+          <t>163757; 219156</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>169272; 225838</t>
+          <t>168292; 224728</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>310377; 426203</t>
+          <t>389668; 458281</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>243028; 305286</t>
+          <t>241953; 304359</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>201501; 263233</t>
+          <t>201473; 259115</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>211255; 274256</t>
+          <t>211793; 273193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>462286; 595804</t>
+          <t>536294; 625187</t>
         </is>
       </c>
     </row>
